--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27135.43</v>
+        <v>27232.27</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>12079.76</v>
+        <v>12211.14</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7037.72</v>
+        <v>7060.87</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15777.24</v>
+        <v>15643.59</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>48262.08</v>
+        <v>48480.79</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11137.31</v>
+        <v>11166.84</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>17732.62</v>
+        <v>17854.68</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6007.44</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8960.049999999999</v>
+        <v>8995.379999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>14239.64</v>
+        <v>14401.58</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12310.94</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8021.18</v>
+        <v>7933.92</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10316.53</v>
+        <v>10350.76</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11105.81</v>
+        <v>11140.15</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7793.42</v>
+        <v>7702.74</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7133.97</v>
+        <v>7094.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1469-3659-CM25</t>
+          <t>1208066-97-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27232.27</v>
+        <v>7001.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2292-9277-CM25</t>
+          <t>1978-519-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>12211.14</v>
+        <v>7746.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1469-3732-CM25</t>
+          <t>1469-3659-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7060.87</v>
+        <v>27232.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>707420-195-CM25</t>
+          <t>2292-9277-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15643.59</v>
+        <v>12211.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1469-4213-CM25</t>
+          <t>1469-3732-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>48480.79</v>
+        <v>7060.87</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1208102-83-CM25</t>
+          <t>707420-195-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11166.84</v>
+        <v>15643.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1495207-5-CM25</t>
+          <t>1469-4213-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>17854.68</v>
+        <v>48480.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3385-8-CM26</t>
+          <t>1208102-83-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>GAMO SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.547.481-5</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6186</v>
+        <v>11166.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4451-121-CM26</t>
+          <t>1495207-5-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8995.379999999999</v>
+        <v>17854.68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1469-903-CM26</t>
+          <t>3385-8-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>GAMO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>77.547.481-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>14401.58</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>4451-121-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>12279.86</v>
+        <v>8995.379999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4511-65-CM26</t>
+          <t>1469-903-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7933.92</v>
+        <v>14401.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3759-543-CM26</t>
+          <t>2177-50-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.130.400-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10350.76</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2291-1118-CM26</t>
+          <t>4511-65-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de Retiro</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11140.15</v>
+        <v>7933.92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1069417-850-CM26</t>
+          <t>3759-543-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.130.400-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7702.74</v>
+        <v>10350.76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2292-6829-CM26</t>
+          <t>2291-1118-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,6 +1484,128 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
+        <v>11140.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1069417-850-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dirección  de Salud Municipal Chillán</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.351.814-9</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>7702.74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2292-6829-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
         <v>7094.42</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1978-519-CM25</t>
+          <t>1208066-112-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7746.66</v>
+        <v>8444.639999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1469-3659-CM25</t>
+          <t>1079566-151-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27232.27</v>
+        <v>10096.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2292-9277-CM25</t>
+          <t>1079566-146-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12211.14</v>
+        <v>7818.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1469-3732-CM25</t>
+          <t>1079566-147-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7060.87</v>
+        <v>9000.709999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>707420-195-CM25</t>
+          <t>2177-48-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>15643.59</v>
+        <v>5805.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1469-4213-CM25</t>
+          <t>2445-2835-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>48480.79</v>
+        <v>16175.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1208102-83-CM25</t>
+          <t>1079566-171-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,28 +996,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>11166.84</v>
+        <v>14867.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1495207-5-CM25</t>
+          <t>1978-519-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,43 +1057,43 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17854.68</v>
+        <v>7746.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3385-8-CM26</t>
+          <t>2292-693-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>GAMO SPA</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.547.481-5</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,43 +1118,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6186</v>
+        <v>15360.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4451-121-CM26</t>
+          <t>2177-59-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8995.379999999999</v>
+        <v>6887.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1469-903-CM26</t>
+          <t>2445-3090-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>14401.58</v>
+        <v>10066.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>1469-2229-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,43 +1301,43 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12279.86</v>
+        <v>7371.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4511-65-CM26</t>
+          <t>1389488-31-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,28 +1362,28 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7933.92</v>
+        <v>5654.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3759-543-CM26</t>
+          <t>4476-187-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.130.400-0</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MUEBLES SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.369.344-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,43 +1423,43 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10350.76</v>
+        <v>5799.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2291-1118-CM26</t>
+          <t>1079566-464-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>PEDRO ANTONIO PEDREROS CONCHA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>10.595.925-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11140.15</v>
+        <v>8347.959999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1069417-850-CM26</t>
+          <t>1469-3659-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7702.74</v>
+        <v>27232.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2292-6829-CM26</t>
+          <t>2292-9277-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,7 +1606,983 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
+        <v>12211.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1469-3732-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>7060.87</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>707420-195-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.404.809-1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>15643.59</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1469-4213-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.625.647-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>48480.79</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1208102-83-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>11166.84</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1495207-5-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>17854.68</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3385-8-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.101.023-0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>GAMO SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.547.481-5</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>6186</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4451-121-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>8995.379999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1469-903-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.625.647-3</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>14401.58</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2177-50-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>12279.86</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4511-65-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.130.800-6</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Retiro</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>COMERCIAL FENIX LTDA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.029.126-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>7933.92</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3759-543-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.130.400-0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>10350.76</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2291-1118-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>11140.15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1069417-850-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dirección  de Salud Municipal Chillán</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.351.814-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>7702.74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2292-6829-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
         <v>7094.42</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4404-177-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>11180.61</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3385-186-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.101.023-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>7103.07</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2177-48-CM25</t>
+          <t>2445-2835-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>suria ltda</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.827.520-1</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5805.92</v>
+        <v>16175.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2445-2835-CM25</t>
+          <t>2177-48-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>suria ltda</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.827.520-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16175.27</v>
+        <v>5805.92</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1469-3732-CM25</t>
+          <t>1389488-70-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7060.87</v>
+        <v>29643.66</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>707420-195-CM25</t>
+          <t>1469-3732-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15643.59</v>
+        <v>7060.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1469-4213-CM25</t>
+          <t>707420-195-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>48480.79</v>
+        <v>15643.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1208102-83-CM25</t>
+          <t>1469-4213-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11166.84</v>
+        <v>48480.79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1495207-5-CM25</t>
+          <t>1208102-83-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>17854.68</v>
+        <v>11166.84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3385-8-CM26</t>
+          <t>1495207-5-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>GAMO SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.547.481-5</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>6186</v>
+        <v>17854.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4451-121-CM26</t>
+          <t>3385-8-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>GAMO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>77.547.481-5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8995.379999999999</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1469-903-CM26</t>
+          <t>1456838-11-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>14401.58</v>
+        <v>6685.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>4451-121-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>12279.86</v>
+        <v>8995.379999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4511-65-CM26</t>
+          <t>1469-903-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7933.92</v>
+        <v>14401.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3759-543-CM26</t>
+          <t>2177-50-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.130.400-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10350.76</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2291-1118-CM26</t>
+          <t>4511-65-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.029.126-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11140.15</v>
+        <v>7933.92</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1069417-850-CM26</t>
+          <t>3759-543-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.130.400-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7702.74</v>
+        <v>10350.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2292-6829-CM26</t>
+          <t>2291-1118-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7094.42</v>
+        <v>11140.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4404-177-CM26</t>
+          <t>2292-6829-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11180.61</v>
+        <v>7094.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3385-186-CM26</t>
+          <t>4404-177-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,6 +2582,67 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
+        <v>11180.61</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3385-186-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.101.023-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
         <v>7103.07</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -562,7 +562,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1960,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2025,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2090,11 @@
           <t>77.547.481-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2216,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2342,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2468,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2594,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2720,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2734,6 +2734,71 @@
         <v>7103.07</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4404-221-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>26391.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2107,7 +2107,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1456838-11-CM26</t>
+          <t>1208066-75-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2122,22 +2122,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.981.440-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2147,28 +2147,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6685.88</v>
+        <v>8042.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4451-121-CM26</t>
+          <t>1456838-11-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2178,12 +2182,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2193,12 +2197,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.981.440-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS CEREZOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2208,32 +2212,28 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8995.379999999999</v>
+        <v>6685.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1469-903-CM26</t>
+          <t>4451-121-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2243,27 +2243,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2273,28 +2273,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>14401.58</v>
+        <v>8995.379999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2177-50-CM26</t>
+          <t>1469-903-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2304,12 +2308,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2319,12 +2323,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2334,32 +2338,28 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.625.647-3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>12279.86</v>
+        <v>14401.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4511-65-CM26</t>
+          <t>2177-50-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2399,28 +2399,32 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL FENIX LTDA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.029.126-9</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7933.92</v>
+        <v>12279.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3759-543-CM26</t>
+          <t>4511-65-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2435,22 +2439,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.130.400-0</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2460,32 +2464,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL FENIX LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.029.126-9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>10350.76</v>
+        <v>7933.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2291-1118-CM26</t>
+          <t>3759-543-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2495,27 +2495,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.400-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2525,28 +2525,32 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11140.15</v>
+        <v>10350.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2292-6829-CM26</t>
+          <t>2291-1118-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2556,17 +2560,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2586,32 +2590,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7094.42</v>
+        <v>11140.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4404-177-CM26</t>
+          <t>2292-6829-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2621,27 +2621,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2651,28 +2651,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>11180.61</v>
+        <v>7094.42</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3385-186-CM26</t>
+          <t>4404-177-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2687,7 +2691,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2697,12 +2701,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2712,90 +2716,151 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7103.07</v>
+        <v>11180.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>3385-186-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.101.023-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>7103.07</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>4404-221-CM26</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2239-4-LR25</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>69.110.500-8</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>MELMAN SPA</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
         <v>26391.61</v>
       </c>
     </row>
